--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487209_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487209_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.3083</v>
+        <v>9.221399999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>9.6097</v>
+        <v>6.0046</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6986</v>
+        <v>3.2168</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2333</v>
@@ -610,13 +610,13 @@
         <v>3.2811</v>
       </c>
       <c r="S2" t="n">
-        <v>7.649</v>
+        <v>3.5621</v>
       </c>
       <c r="T2" t="n">
-        <v>6.0045</v>
+        <v>2.3995</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6445</v>
+        <v>1.1626</v>
       </c>
       <c r="V2" t="n">
         <v>4.5415</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.008</v>
+        <v>8.023300000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0691</v>
+        <v>5.8702</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9389</v>
+        <v>2.1531</v>
       </c>
       <c r="G3" t="n">
         <v>3.3066</v>
@@ -688,13 +688,13 @@
         <v>2.8951</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5433</v>
+        <v>1.5586</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2195</v>
+        <v>1.0206</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3238</v>
+        <v>0.538</v>
       </c>
       <c r="V3" t="n">
         <v>1.228</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3812</v>
+        <v>5.2626</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4802</v>
+        <v>3.2813</v>
       </c>
       <c r="F4" t="n">
-        <v>1.901</v>
+        <v>1.9813</v>
       </c>
       <c r="G4" t="n">
         <v>4.1492</v>
@@ -766,13 +766,13 @@
         <v>2.1231</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.926</v>
+        <v>-0.0446</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8037</v>
+        <v>-0.0026</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1223</v>
+        <v>-0.042</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6931</v>
+        <v>2.6723</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2519</v>
+        <v>0.0485</v>
       </c>
       <c r="F5" t="n">
-        <v>2.945</v>
+        <v>2.6238</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2698</v>
@@ -844,13 +844,13 @@
         <v>2.7021</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2717</v>
+        <v>1.2509</v>
       </c>
       <c r="T5" t="n">
-        <v>0.279</v>
+        <v>0.5794</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9928</v>
+        <v>0.6715</v>
       </c>
       <c r="V5" t="n">
         <v>1.8842</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>C. POLANCO MERINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3355</v>
+        <v>2.2074</v>
       </c>
       <c r="E6" t="n">
-        <v>2.493</v>
+        <v>0.0206</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1575</v>
+        <v>2.1869</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6993</v>
+        <v>0.3335</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7743</v>
+        <v>-0.6697</v>
       </c>
       <c r="I6" t="n">
-        <v>0.075</v>
+        <v>1.0032</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3229</v>
+        <v>-0.7416</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6881</v>
+        <v>-0.1554</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6348</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0222</v>
+        <v>1.0751</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4624</v>
+        <v>-0.5143</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5598</v>
+        <v>1.5894</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.772</v>
+        <v>1.158</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>1.158</v>
       </c>
       <c r="S6" t="n">
-        <v>2.521</v>
+        <v>1.0017</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5864</v>
+        <v>0.7621</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9346</v>
+        <v>0.2396</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2859</v>
+        <v>-0.2859</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8695000000000001</v>
+        <v>1.3434</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1656</v>
+        <v>-0.6649</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0351</v>
+        <v>2.0083</v>
       </c>
       <c r="G7" t="n">
         <v>0.8742</v>
@@ -1000,13 +1000,13 @@
         <v>1.158</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2399</v>
+        <v>0.234</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4468</v>
+        <v>0.0539</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2069</v>
+        <v>0.1801</v>
       </c>
       <c r="V7" t="n">
         <v>0.0422</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. POLANCO MERINO</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2969</v>
+        <v>0.1061</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3814</v>
+        <v>1.6919</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6782</v>
+        <v>-1.5858</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3335</v>
+        <v>-0.6993</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6697</v>
+        <v>-0.7743</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0032</v>
+        <v>0.075</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7416</v>
+        <v>1.3229</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1554</v>
+        <v>0.6881</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.6348</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0751</v>
+        <v>-2.0222</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5143</v>
+        <v>-1.4624</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5894</v>
+        <v>-0.5598</v>
       </c>
       <c r="P8" t="n">
-        <v>1.158</v>
+        <v>-0.772</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R8" t="n">
         <v>1.158</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9089</v>
+        <v>1.2916</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6398</v>
+        <v>0.7853</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.269</v>
+        <v>0.5063</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2859</v>
+        <v>0.2859</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4179</v>
+        <v>-1.3644</v>
       </c>
       <c r="E9" t="n">
         <v>-1.5137</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1493</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7411</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.6233</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1785</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4984</v>
+        <v>-0.4449</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8361</v>
+        <v>-1.4752</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0814</v>
+        <v>-0.8811</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7547</v>
+        <v>-0.5941</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4528</v>
@@ -1234,13 +1234,13 @@
         <v>0.386</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7694</v>
+        <v>-0.4085</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4759</v>
+        <v>-0.2756</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2935</v>
+        <v>-0.1329</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4196</v>
+        <v>-2.0587</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.772</v>
+        <v>-1.5718</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6476</v>
+        <v>-0.487</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4384</v>
@@ -1312,13 +1312,13 @@
         <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3093</v>
+        <v>0.0516</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2829</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0264</v>
+        <v>0.1342</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2859</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8298</v>
+        <v>-2.5492</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2762</v>
+        <v>-3.076</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4465</v>
+        <v>0.5268</v>
       </c>
       <c r="G12" t="n">
         <v>-1.622</v>
@@ -1390,13 +1390,13 @@
         <v>0.965</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.659</v>
+        <v>-0.3784</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1652</v>
+        <v>0.0351</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4938</v>
+        <v>-0.4135</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5138</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.3891</v>
+        <v>21.389</v>
       </c>
       <c r="E13" t="n">
-        <v>9.2098</v>
+        <v>9.2096</v>
       </c>
       <c r="F13" t="n">
-        <v>12.1792</v>
+        <v>12.1794</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2068</v>
+        <v>2.206800000000001</v>
       </c>
       <c r="H13" t="n">
         <v>-5.739999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>16.4054</v>
       </c>
       <c r="S13" t="n">
-        <v>7.4956</v>
+        <v>7.495699999999999</v>
       </c>
       <c r="T13" t="n">
         <v>5.0966</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3992</v>
+        <v>2.399</v>
       </c>
       <c r="V13" t="n">
         <v>5.8962</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>C. HERRERO SANDOVAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7536</v>
+        <v>0.4457</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1904</v>
+        <v>0.3953</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4369</v>
+        <v>0.0504</v>
       </c>
       <c r="G14" t="n">
-        <v>0.756</v>
+        <v>-0.525</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5614</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.8054</v>
+        <v>0.0814</v>
       </c>
       <c r="J14" t="n">
-        <v>2.6646</v>
+        <v>-0.2917</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4967</v>
+        <v>-0.2588</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.8321</v>
+        <v>-0.0328</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9086</v>
+        <v>-0.2333</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9353</v>
+        <v>-0.3476</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9732</v>
+        <v>0.1142</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.386</v>
+        <v>0.772</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5441</v>
+        <v>0.772</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0398</v>
+        <v>-1.3996</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9843</v>
+        <v>-0.541</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0555</v>
+        <v>-0.8587</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6562</v>
+        <v>1.5983</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4716</v>
+        <v>1.228</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.1278</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0034</v>
+        <v>0.0503</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0282</v>
+        <v>0.7278</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0249</v>
+        <v>-0.6775</v>
       </c>
       <c r="G15" t="n">
         <v>1.4725</v>
@@ -1624,13 +1624,13 @@
         <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.199</v>
+        <v>-0.152</v>
       </c>
       <c r="T15" t="n">
-        <v>0.427</v>
+        <v>0.1266</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.626</v>
+        <v>-0.2786</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2702</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. HERRERO SANDOVAL</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3227</v>
+        <v>-0.3639</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1054</v>
+        <v>2.2878</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2173</v>
+        <v>-2.6517</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.525</v>
+        <v>0.756</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6064000000000001</v>
+        <v>3.5614</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0814</v>
+        <v>-2.8054</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2917</v>
+        <v>2.6646</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2588</v>
+        <v>4.4967</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0328</v>
+        <v>-1.8321</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2333</v>
+        <v>-1.9086</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3476</v>
+        <v>-0.9353</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1142</v>
+        <v>-0.9732</v>
       </c>
       <c r="P16" t="n">
-        <v>0.772</v>
+        <v>-0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>0.772</v>
+        <v>1.5441</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.168</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0417</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1263</v>
+        <v>-0.1593</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5983</v>
+        <v>-0.6562</v>
       </c>
       <c r="W16" t="n">
-        <v>1.228</v>
+        <v>1.4716</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3704</v>
+        <v>-2.1278</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4791</v>
+        <v>-0.9979</v>
       </c>
       <c r="E17" t="n">
         <v>0.9443</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4233</v>
+        <v>-1.9421</v>
       </c>
       <c r="G17" t="n">
         <v>1.696</v>
@@ -1780,13 +1780,13 @@
         <v>0.193</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9122</v>
+        <v>-0.431</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0172</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.895</v>
+        <v>-0.4138</v>
       </c>
       <c r="V17" t="n">
         <v>-2.4559</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MASSALEY JR</t>
+          <t>J. MORAN HUETE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2968</v>
+        <v>-1.3174</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5353</v>
+        <v>1.3252</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2385</v>
+        <v>-2.6426</v>
       </c>
       <c r="G18" t="n">
-        <v>4.0976</v>
+        <v>0.5447</v>
       </c>
       <c r="H18" t="n">
-        <v>2.776</v>
+        <v>-2.195</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3217</v>
+        <v>2.7397</v>
       </c>
       <c r="J18" t="n">
-        <v>5.5257</v>
+        <v>2.0999</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6378</v>
+        <v>-1.0661</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8879</v>
+        <v>3.166</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4281</v>
+        <v>-1.5552</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8619</v>
+        <v>-1.1289</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5662</v>
+        <v>-0.4263</v>
       </c>
       <c r="P18" t="n">
-        <v>-5.5972</v>
+        <v>2.1231</v>
       </c>
       <c r="Q18" t="n">
-        <v>-7.7203</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>2.1231</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7972</v>
+        <v>-1.5292</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6266</v>
+        <v>-0.7746</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1706</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.4559</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2859</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MORAN HUETE</t>
+          <t>A. MASSALEY JR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3601</v>
+        <v>-2.538</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9247</v>
+        <v>-2.5353</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.2847</v>
+        <v>-0.0027</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5447</v>
+        <v>4.0976</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.195</v>
+        <v>2.776</v>
       </c>
       <c r="I19" t="n">
-        <v>2.7397</v>
+        <v>1.3217</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0999</v>
+        <v>5.5257</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0661</v>
+        <v>3.6378</v>
       </c>
       <c r="L19" t="n">
-        <v>3.166</v>
+        <v>1.8879</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5552</v>
+        <v>-1.4281</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1289</v>
+        <v>-0.8619</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4263</v>
+        <v>-0.5662</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1231</v>
+        <v>-5.5972</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-7.7203</v>
       </c>
       <c r="R19" t="n">
         <v>2.1231</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.5719</v>
+        <v>-1.0384</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1752</v>
+        <v>-0.6266</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.3967</v>
+        <v>-0.4118</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.4559</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4559</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3378</v>
+        <v>-3.5965</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9825</v>
+        <v>-3.4818</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3553</v>
+        <v>-0.1147</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3049</v>
@@ -2014,13 +2014,13 @@
         <v>0.193</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5467</v>
+        <v>-0.8054</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7442</v>
+        <v>-0.2435</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8025</v>
+        <v>-0.5619</v>
       </c>
       <c r="V20" t="n">
         <v>0.2859</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8071</v>
+        <v>-4.4336</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.2786</v>
+        <v>-4.878</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4715</v>
+        <v>0.4444</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4738</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4032</v>
+        <v>-0.0297</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3873</v>
+        <v>0.0132</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0159</v>
+        <v>-0.043</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.5425</v>
+        <v>-7.3025</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.7512</v>
+        <v>-6.3506</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7913</v>
+        <v>-0.9519</v>
       </c>
       <c r="G22" t="n">
         <v>-5.4701</v>
@@ -2170,13 +2170,13 @@
         <v>1.7371</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9373</v>
+        <v>-0.6973</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8183</v>
+        <v>-0.4177</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.119</v>
+        <v>-0.2796</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9421</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-21.3891</v>
+        <v>-20.0538</v>
       </c>
       <c r="E23" t="n">
-        <v>-11.5654</v>
+        <v>-11.5653</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.823699999999999</v>
+        <v>-8.4884</v>
       </c>
       <c r="G23" t="n">
         <v>-2.207000000000002</v>
@@ -2218,7 +2218,7 @@
         <v>5.7401</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.9469</v>
+        <v>-7.946899999999999</v>
       </c>
       <c r="J23" t="n">
         <v>2.496699999999999</v>
@@ -2248,13 +2248,13 @@
         <v>10.6155</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.495699999999999</v>
+        <v>-6.160299999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.3992</v>
+        <v>-2.3991</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.0965</v>
+        <v>-3.7612</v>
       </c>
       <c r="V23" t="n">
         <v>-5.896100000000001</v>
